--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>196</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7394,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8703,7 +8703,7 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9111,7 +9111,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9366,7 +9366,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10964,7 +10964,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13497,7 +13497,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13803,7 +13803,7 @@
         <v>7</v>
       </c>
       <c r="D573">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E573" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14109,7 +14109,7 @@
         <v>7</v>
       </c>
       <c r="D591">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E591" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15367,7 +15367,7 @@
         <v>7</v>
       </c>
       <c r="D665">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E665" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16081,7 +16081,7 @@
         <v>7</v>
       </c>
       <c r="D707">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E707" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16608,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17254,7 +17254,7 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E776" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19719,7 +19719,7 @@
         <v>7</v>
       </c>
       <c r="D921">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E921" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20569,7 +20569,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21929,7 +21929,7 @@
         <v>7</v>
       </c>
       <c r="D1051">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1051" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>254</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>316</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8703,7 +8703,7 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10114,7 +10114,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10913,7 +10913,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12052,7 +12052,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12477,7 +12477,7 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13497,7 +13497,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15367,7 +15367,7 @@
         <v>7</v>
       </c>
       <c r="D665">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E665" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15979,7 +15979,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16081,7 +16081,7 @@
         <v>7</v>
       </c>
       <c r="D707">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E707" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17254,7 +17254,7 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E776" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17560,7 +17560,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19719,7 +19719,7 @@
         <v>7</v>
       </c>
       <c r="D921">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E921" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20569,7 +20569,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21929,7 +21929,7 @@
         <v>7</v>
       </c>
       <c r="D1051">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1051" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22779,7 +22779,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>359</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>78</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7394,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8244,7 +8244,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8703,7 +8703,7 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9111,7 +9111,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10114,7 +10114,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10964,7 +10964,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11848,7 +11848,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12477,7 +12477,7 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15367,7 +15367,7 @@
         <v>7</v>
       </c>
       <c r="D665">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E665" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16608,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17254,7 +17254,7 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E776" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17560,7 +17560,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18291,7 +18291,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20569,7 +20569,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21929,7 +21929,7 @@
         <v>7</v>
       </c>
       <c r="D1051">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1051" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>117</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>77</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>75</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>70</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>209</v>
+        <v>310</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8244,7 +8244,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9366,7 +9366,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10913,7 +10913,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10964,7 +10964,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11848,7 +11848,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14109,7 +14109,7 @@
         <v>7</v>
       </c>
       <c r="D591">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E591" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15979,7 +15979,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16608,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17254,7 +17254,7 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E776" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20569,7 +20569,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21929,7 +21929,7 @@
         <v>7</v>
       </c>
       <c r="D1051">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1051" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22779,7 +22779,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>265</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>49</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>49</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>87</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>69</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>310</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7394,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9111,7 +9111,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10114,7 +10114,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10913,7 +10913,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11848,7 +11848,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12052,7 +12052,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13497,7 +13497,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13803,7 +13803,7 @@
         <v>7</v>
       </c>
       <c r="D573">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E573" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14109,7 +14109,7 @@
         <v>7</v>
       </c>
       <c r="D591">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E591" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16081,7 +16081,7 @@
         <v>7</v>
       </c>
       <c r="D707">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E707" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16608,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17560,7 +17560,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18291,7 +18291,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19719,7 +19719,7 @@
         <v>7</v>
       </c>
       <c r="D921">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E921" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21929,7 +21929,7 @@
         <v>7</v>
       </c>
       <c r="D1051">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1051" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22779,7 +22779,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>365</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>44</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7394,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8244,7 +8244,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9366,7 +9366,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10114,7 +10114,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10913,7 +10913,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11848,7 +11848,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12052,7 +12052,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12477,7 +12477,7 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13497,7 +13497,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14109,7 +14109,7 @@
         <v>7</v>
       </c>
       <c r="D591">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E591" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15367,7 +15367,7 @@
         <v>7</v>
       </c>
       <c r="D665">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E665" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15979,7 +15979,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16608,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18291,7 +18291,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19719,7 +19719,7 @@
         <v>7</v>
       </c>
       <c r="D921">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E921" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20569,7 +20569,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>59</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>53</v>
+        <v>333</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7394,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8244,7 +8244,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9366,7 +9366,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10114,7 +10114,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10913,7 +10913,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10964,7 +10964,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11848,7 +11848,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12052,7 +12052,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12477,7 +12477,7 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13803,7 +13803,7 @@
         <v>7</v>
       </c>
       <c r="D573">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E573" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14109,7 +14109,7 @@
         <v>7</v>
       </c>
       <c r="D591">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E591" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15979,7 +15979,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16081,7 +16081,7 @@
         <v>7</v>
       </c>
       <c r="D707">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E707" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16608,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17254,7 +17254,7 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E776" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18291,7 +18291,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21929,7 +21929,7 @@
         <v>7</v>
       </c>
       <c r="D1051">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1051" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22779,7 +22779,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>108</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>333</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7394,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8703,7 +8703,7 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9366,7 +9366,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10080,7 +10080,7 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10913,7 +10913,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11848,7 +11848,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12052,7 +12052,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13497,7 +13497,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14109,7 +14109,7 @@
         <v>7</v>
       </c>
       <c r="D591">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E591" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15367,7 +15367,7 @@
         <v>7</v>
       </c>
       <c r="D665">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E665" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15979,7 +15979,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16081,7 +16081,7 @@
         <v>7</v>
       </c>
       <c r="D707">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E707" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17254,7 +17254,7 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E776" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17560,7 +17560,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19719,7 +19719,7 @@
         <v>7</v>
       </c>
       <c r="D921">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E921" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>389</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>75</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>77</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>70</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8244,7 +8244,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8703,7 +8703,7 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9111,7 +9111,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9366,7 +9366,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10029,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10913,7 +10913,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10964,7 +10964,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11202,7 +11202,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12052,7 +12052,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12477,7 +12477,7 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12664,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13497,7 +13497,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13803,7 +13803,7 @@
         <v>7</v>
       </c>
       <c r="D573">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E573" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15979,7 +15979,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16081,7 +16081,7 @@
         <v>7</v>
       </c>
       <c r="D707">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E707" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16625,7 +16625,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17560,7 +17560,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18291,7 +18291,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19362,7 +19362,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19787,7 +19787,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20348,7 +20348,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21334,7 +21334,7 @@
         <v>7</v>
       </c>
       <c r="D1016">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1016" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21708,7 +21708,7 @@
         <v>7</v>
       </c>
       <c r="D1038">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1038" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21929,7 +21929,7 @@
         <v>7</v>
       </c>
       <c r="D1051">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1051" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22779,7 +22779,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>138</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>70</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>213</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5235,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5609,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5626,7 +5626,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6867,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7462,7 +7462,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7479,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8244,7 +8244,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8363,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8601,7 +8601,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8720,7 +8720,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8856,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9060,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9111,7 +9111,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9366,7 +9366,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9621,7 +9621,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9655,7 +9655,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9927,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9961,7 +9961,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10114,7 +10114,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10131,7 +10131,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10692,7 +10692,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10964,7 +10964,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11083,7 +11083,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11508,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11865,7 +11865,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -12001,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12222,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12307,7 +12307,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12800,7 +12800,7 @@
         <v>7</v>
       </c>
       <c r="D514">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13259,7 +13259,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E543" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13429,7 +13429,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13548,7 +13548,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13752,7 +13752,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13939,7 +13939,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14432,7 +14432,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14534,7 +14534,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14755,7 +14755,7 @@
         <v>7</v>
       </c>
       <c r="D629">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E629" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14942,7 +14942,7 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E640" t="s">
         <v>8</v>
@@ -14959,7 +14959,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15010,7 +15010,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15197,7 +15197,7 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E655" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D683">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E683" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15741,7 +15741,7 @@
         <v>7</v>
       </c>
       <c r="D687">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E687" t="s">
         <v>8</v>
@@ -15758,7 +15758,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15979,7 +15979,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -15996,7 +15996,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16115,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16336,7 +16336,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16455,7 +16455,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16642,7 +16642,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16846,7 +16846,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17050,7 +17050,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17152,7 +17152,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17288,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17475,7 +17475,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17560,7 +17560,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17747,7 +17747,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18036,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18155,7 +18155,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18206,7 +18206,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18240,7 +18240,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18291,7 +18291,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18359,7 +18359,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18648,7 +18648,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18665,7 +18665,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18920,7 +18920,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19005,7 +19005,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19277,7 +19277,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19345,7 +19345,7 @@
         <v>7</v>
       </c>
       <c r="D899">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E899" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19464,7 +19464,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19634,7 +19634,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19668,7 +19668,7 @@
         <v>7</v>
       </c>
       <c r="D918">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E918" t="s">
         <v>8</v>
@@ -19685,7 +19685,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19838,7 +19838,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19872,7 +19872,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20042,7 +20042,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20569,7 +20569,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20603,7 +20603,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20977,7 +20977,7 @@
         <v>7</v>
       </c>
       <c r="D995">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E995" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21011,7 +21011,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21844,7 +21844,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21878,7 +21878,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21912,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22031,7 +22031,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22082,7 +22082,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22779,7 +22779,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>281</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23386,7 +23386,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4895,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5150,7 +5150,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5167,7 +5167,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5184,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5252,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5269,7 +5269,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5303,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5337,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5371,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5388,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5405,7 +5405,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5422,7 +5422,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5456,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5490,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5524,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5660,7 +5660,7 @@
         <v>7</v>
       </c>
       <c r="D94">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5711,7 +5711,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5779,7 +5779,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5864,7 +5864,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5915,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5932,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -5966,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6017,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6051,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6068,7 +6068,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6102,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6119,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6136,7 +6136,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6153,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6170,7 +6170,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6221,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6238,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6272,7 +6272,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6289,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6357,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6391,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6425,7 +6425,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6442,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6459,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6476,7 +6476,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6493,7 +6493,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6544,7 +6544,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6561,7 +6561,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6612,7 +6612,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6629,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6663,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6680,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6697,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6714,7 +6714,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6731,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6816,7 +6816,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6833,7 +6833,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6850,7 +6850,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6918,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6935,7 +6935,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6969,7 +6969,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6986,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7003,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7020,7 +7020,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7037,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7088,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7105,7 +7105,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7122,7 +7122,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7139,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7156,7 +7156,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7258,7 +7258,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7275,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7292,7 +7292,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7309,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7326,7 +7326,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7360,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7377,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7411,7 +7411,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7428,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7513,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7530,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7581,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7615,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7700,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7717,7 +7717,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7734,7 +7734,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7751,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7768,7 +7768,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7802,7 +7802,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7819,7 +7819,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7836,7 +7836,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7853,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7870,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7904,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7938,7 +7938,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7955,7 +7955,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7972,7 +7972,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7989,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8006,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8023,7 +8023,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8040,7 +8040,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8057,7 +8057,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8142,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8176,7 +8176,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8210,7 +8210,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8227,7 +8227,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8244,7 +8244,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8261,7 +8261,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8278,7 +8278,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8295,7 +8295,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8312,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8346,7 +8346,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8380,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8397,7 +8397,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8431,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8448,7 +8448,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8465,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8482,7 +8482,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8499,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8516,7 +8516,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8550,7 +8550,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8567,7 +8567,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8584,7 +8584,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8652,7 +8652,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8686,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8703,7 +8703,7 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8737,7 +8737,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8771,7 +8771,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8839,7 +8839,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8890,7 +8890,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8924,7 +8924,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8958,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8992,7 +8992,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -9009,7 +9009,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9026,7 +9026,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9043,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9094,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9111,7 +9111,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9128,7 +9128,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9145,7 +9145,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9162,7 +9162,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9179,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9196,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9213,7 +9213,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9230,7 +9230,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9264,7 +9264,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9298,7 +9298,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9315,7 +9315,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9332,7 +9332,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9349,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9383,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9451,7 +9451,7 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -9468,7 +9468,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9519,7 +9519,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9536,7 +9536,7 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9570,7 +9570,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9587,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9604,7 +9604,7 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9672,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9689,7 +9689,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9706,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9723,7 +9723,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9740,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="D334">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9757,7 +9757,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9774,7 +9774,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9808,7 +9808,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9842,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9876,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="D343">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -9910,7 +9910,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -9995,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="D349">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10046,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10063,7 +10063,7 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10097,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10114,7 +10114,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10148,7 +10148,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10233,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10267,7 +10267,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10318,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10335,7 +10335,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10369,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10386,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10403,7 +10403,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10420,7 +10420,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10454,7 +10454,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10488,7 +10488,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10505,7 +10505,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10522,7 +10522,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10556,7 +10556,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10573,7 +10573,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10607,7 +10607,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10624,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="D388">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10675,7 +10675,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10709,7 +10709,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10726,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10760,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="D394">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E394" t="s">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10794,7 +10794,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10811,7 +10811,7 @@
         <v>7</v>
       </c>
       <c r="D397">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -10828,7 +10828,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10845,7 +10845,7 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -10862,7 +10862,7 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -10879,7 +10879,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10930,7 +10930,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -10947,7 +10947,7 @@
         <v>7</v>
       </c>
       <c r="D405">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -10964,7 +10964,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10981,7 +10981,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11032,7 +11032,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11066,7 +11066,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11117,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E415" t="s">
         <v>8</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11151,7 +11151,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11168,7 +11168,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11219,7 +11219,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11236,7 +11236,7 @@
         <v>7</v>
       </c>
       <c r="D422">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11253,7 +11253,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11304,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11321,7 +11321,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11338,7 +11338,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11355,7 +11355,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11372,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11423,7 +11423,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11440,7 +11440,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11457,7 +11457,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11491,7 +11491,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11525,7 +11525,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11542,7 +11542,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11576,7 +11576,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11678,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11695,7 +11695,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11712,7 +11712,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11729,7 +11729,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11746,7 +11746,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11763,7 +11763,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11780,7 +11780,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11797,7 +11797,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11814,7 +11814,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11831,7 +11831,7 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -11848,7 +11848,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11882,7 +11882,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11899,7 +11899,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11916,7 +11916,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11933,7 +11933,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11950,7 +11950,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11967,7 +11967,7 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -11984,7 +11984,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12035,7 +12035,7 @@
         <v>7</v>
       </c>
       <c r="D469">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12052,7 +12052,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7</v>
       </c>
       <c r="D471">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12086,7 +12086,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12103,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12120,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12137,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D476">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12171,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12188,7 +12188,7 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12256,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12324,7 +12324,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12341,7 +12341,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12358,7 +12358,7 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12375,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12392,7 +12392,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12426,7 +12426,7 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12443,7 +12443,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12460,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12477,7 +12477,7 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12494,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12528,7 +12528,7 @@
         <v>7</v>
       </c>
       <c r="D498">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12545,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12562,7 +12562,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12579,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12630,7 +12630,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12647,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12681,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12698,7 +12698,7 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12715,7 +12715,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12749,7 +12749,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12766,7 +12766,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12783,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12834,7 +12834,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -12851,7 +12851,7 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -12868,7 +12868,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -12885,7 +12885,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12902,7 +12902,7 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -12919,7 +12919,7 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -12936,7 +12936,7 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12970,7 +12970,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13004,7 +13004,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13021,7 +13021,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13038,7 +13038,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13055,7 +13055,7 @@
         <v>7</v>
       </c>
       <c r="D529">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13072,7 +13072,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13089,7 +13089,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13106,7 +13106,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13123,7 +13123,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13157,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13174,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13191,7 +13191,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13208,7 +13208,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13242,7 +13242,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13276,7 +13276,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13310,7 +13310,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13327,7 +13327,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13344,7 +13344,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13361,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13378,7 +13378,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13412,7 +13412,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13446,7 +13446,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13463,7 +13463,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13480,7 +13480,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13497,7 +13497,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13514,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13565,7 +13565,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13582,7 +13582,7 @@
         <v>7</v>
       </c>
       <c r="D560">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E560" t="s">
         <v>8</v>
@@ -13599,7 +13599,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13616,7 +13616,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13633,7 +13633,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13650,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13735,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13769,7 +13769,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13803,7 +13803,7 @@
         <v>7</v>
       </c>
       <c r="D573">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E573" t="s">
         <v>8</v>
@@ -13820,7 +13820,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13871,7 +13871,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13888,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13922,7 +13922,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13956,7 +13956,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13973,7 +13973,7 @@
         <v>7</v>
       </c>
       <c r="D583">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E583" t="s">
         <v>8</v>
@@ -13990,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E585" t="s">
         <v>8</v>
@@ -14024,7 +14024,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14058,7 +14058,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E588" t="s">
         <v>8</v>
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14092,7 +14092,7 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E590" t="s">
         <v>8</v>
@@ -14126,7 +14126,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14143,7 +14143,7 @@
         <v>7</v>
       </c>
       <c r="D593">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E593" t="s">
         <v>8</v>
@@ -14160,7 +14160,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="D595">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E595" t="s">
         <v>8</v>
@@ -14194,7 +14194,7 @@
         <v>7</v>
       </c>
       <c r="D596">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E596" t="s">
         <v>8</v>
@@ -14211,7 +14211,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14228,7 +14228,7 @@
         <v>7</v>
       </c>
       <c r="D598">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E598" t="s">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14313,7 +14313,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14330,7 +14330,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14347,7 +14347,7 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E605" t="s">
         <v>8</v>
@@ -14364,7 +14364,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14398,7 +14398,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14415,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E609" t="s">
         <v>8</v>
@@ -14449,7 +14449,7 @@
         <v>7</v>
       </c>
       <c r="D611">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E611" t="s">
         <v>8</v>
@@ -14466,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14483,7 +14483,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14500,7 +14500,7 @@
         <v>7</v>
       </c>
       <c r="D614">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E614" t="s">
         <v>8</v>
@@ -14517,7 +14517,7 @@
         <v>7</v>
       </c>
       <c r="D615">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E615" t="s">
         <v>8</v>
@@ -14551,7 +14551,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14568,7 +14568,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E618" t="s">
         <v>8</v>
@@ -14585,7 +14585,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14602,7 +14602,7 @@
         <v>7</v>
       </c>
       <c r="D620">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E620" t="s">
         <v>8</v>
@@ -14619,7 +14619,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14636,7 +14636,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14653,7 +14653,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E623" t="s">
         <v>8</v>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14687,7 +14687,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14704,7 +14704,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14738,7 +14738,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14772,7 +14772,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14789,7 +14789,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14806,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14823,7 +14823,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14840,7 +14840,7 @@
         <v>7</v>
       </c>
       <c r="D634">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E634" t="s">
         <v>8</v>
@@ -14857,7 +14857,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14874,7 +14874,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14891,7 +14891,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14908,7 +14908,7 @@
         <v>7</v>
       </c>
       <c r="D638">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E638" t="s">
         <v>8</v>
@@ -14925,7 +14925,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14976,7 +14976,7 @@
         <v>7</v>
       </c>
       <c r="D642">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E642" t="s">
         <v>8</v>
@@ -14993,7 +14993,7 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E643" t="s">
         <v>8</v>
@@ -15027,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15061,7 +15061,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D648">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E648" t="s">
         <v>8</v>
@@ -15095,7 +15095,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15112,7 +15112,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E650" t="s">
         <v>8</v>
@@ -15129,7 +15129,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15146,7 +15146,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15180,7 +15180,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E656" t="s">
         <v>8</v>
@@ -15231,7 +15231,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15248,7 +15248,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15265,7 +15265,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15282,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15299,7 +15299,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15316,7 +15316,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15350,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15367,7 +15367,7 @@
         <v>7</v>
       </c>
       <c r="D665">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E665" t="s">
         <v>8</v>
@@ -15384,7 +15384,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15401,7 +15401,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15418,7 +15418,7 @@
         <v>7</v>
       </c>
       <c r="D668">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E668" t="s">
         <v>8</v>
@@ -15435,7 +15435,7 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E669" t="s">
         <v>8</v>
@@ -15452,7 +15452,7 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E670" t="s">
         <v>8</v>
@@ -15469,7 +15469,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15503,7 +15503,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="D675">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E675" t="s">
         <v>8</v>
@@ -15554,7 +15554,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15571,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15588,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15622,7 +15622,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15639,7 +15639,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E681" t="s">
         <v>8</v>
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E682" t="s">
         <v>8</v>
@@ -15690,7 +15690,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15707,7 +15707,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E685" t="s">
         <v>8</v>
@@ -15775,7 +15775,7 @@
         <v>7</v>
       </c>
       <c r="D689">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E689" t="s">
         <v>8</v>
@@ -15792,7 +15792,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15809,7 +15809,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15826,7 +15826,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15843,7 +15843,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15860,7 +15860,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15877,7 +15877,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15911,7 +15911,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15928,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15945,7 +15945,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15962,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -16013,7 +16013,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16030,7 +16030,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16064,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16098,7 +16098,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16149,7 +16149,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16183,7 +16183,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16217,7 +16217,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16234,7 +16234,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16251,7 +16251,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16268,7 +16268,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16285,7 +16285,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16319,7 +16319,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16353,7 +16353,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16370,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16387,7 +16387,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16404,7 +16404,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16421,7 +16421,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16438,7 +16438,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16472,7 +16472,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16506,7 +16506,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16523,7 +16523,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16540,7 +16540,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16574,7 +16574,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16591,7 +16591,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16608,7 +16608,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16676,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16710,7 +16710,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16727,7 +16727,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16744,7 +16744,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16761,7 +16761,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16778,7 +16778,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16795,7 +16795,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16812,7 +16812,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16829,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16863,7 +16863,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16880,7 +16880,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16897,7 +16897,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16914,7 +16914,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16948,7 +16948,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16965,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16999,7 +16999,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17016,7 +17016,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17033,7 +17033,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17067,7 +17067,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17084,7 +17084,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17101,7 +17101,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17118,7 +17118,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17135,7 +17135,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17169,7 +17169,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17186,7 +17186,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17220,7 +17220,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17237,7 +17237,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17271,7 +17271,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17305,7 +17305,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17322,7 +17322,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17339,7 +17339,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17390,7 +17390,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17407,7 +17407,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17424,7 +17424,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17441,7 +17441,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17458,7 +17458,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17492,7 +17492,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17509,7 +17509,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17526,7 +17526,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17543,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17560,7 +17560,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17577,7 +17577,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17594,7 +17594,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17611,7 +17611,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17628,7 +17628,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17645,7 +17645,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17662,7 +17662,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17679,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17696,7 +17696,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17713,7 +17713,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17730,7 +17730,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17764,7 +17764,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17781,7 +17781,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17832,7 +17832,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17849,7 +17849,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17866,7 +17866,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17883,7 +17883,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17900,7 +17900,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17917,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17934,7 +17934,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17951,7 +17951,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17968,7 +17968,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17985,7 +17985,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -18002,7 +18002,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18053,7 +18053,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18070,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18087,7 +18087,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18104,7 +18104,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18121,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18138,7 +18138,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18172,7 +18172,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18189,7 +18189,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18223,7 +18223,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18274,7 +18274,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18291,7 +18291,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18308,7 +18308,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18325,7 +18325,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18342,7 +18342,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18376,7 +18376,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18393,7 +18393,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18410,7 +18410,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18427,7 +18427,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18444,7 +18444,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18478,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18495,7 +18495,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18512,7 +18512,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18529,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18546,7 +18546,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18563,7 +18563,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18580,7 +18580,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18597,7 +18597,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18614,7 +18614,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18682,7 +18682,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18716,7 +18716,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18750,7 +18750,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18767,7 +18767,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18784,7 +18784,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18801,7 +18801,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18818,7 +18818,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18835,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18852,7 +18852,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18869,7 +18869,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18886,7 +18886,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18903,7 +18903,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18937,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18954,7 +18954,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18971,7 +18971,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18988,7 +18988,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -19022,7 +19022,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19039,7 +19039,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19056,7 +19056,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E882" t="s">
         <v>8</v>
@@ -19073,7 +19073,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19090,7 +19090,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19107,7 +19107,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19124,7 +19124,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19158,7 +19158,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E888" t="s">
         <v>8</v>
@@ -19175,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="D889">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E889" t="s">
         <v>8</v>
@@ -19192,7 +19192,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19209,7 +19209,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19226,7 +19226,7 @@
         <v>7</v>
       </c>
       <c r="D892">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E892" t="s">
         <v>8</v>
@@ -19243,7 +19243,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19260,7 +19260,7 @@
         <v>7</v>
       </c>
       <c r="D894">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E894" t="s">
         <v>8</v>
@@ -19294,7 +19294,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19311,7 +19311,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19328,7 +19328,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19379,7 +19379,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19396,7 +19396,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19413,7 +19413,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19430,7 +19430,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19447,7 +19447,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19481,7 +19481,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19498,7 +19498,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19515,7 +19515,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19532,7 +19532,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19566,7 +19566,7 @@
         <v>7</v>
       </c>
       <c r="D912">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E912" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19600,7 +19600,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19617,7 +19617,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19702,7 +19702,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19719,7 +19719,7 @@
         <v>7</v>
       </c>
       <c r="D921">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E921" t="s">
         <v>8</v>
@@ -19736,7 +19736,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19753,7 +19753,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19770,7 +19770,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19804,7 +19804,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19821,7 +19821,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19855,7 +19855,7 @@
         <v>7</v>
       </c>
       <c r="D929">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E929" t="s">
         <v>8</v>
@@ -19889,7 +19889,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19906,7 +19906,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E932" t="s">
         <v>8</v>
@@ -19923,7 +19923,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19940,7 +19940,7 @@
         <v>7</v>
       </c>
       <c r="D934">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E934" t="s">
         <v>8</v>
@@ -19957,7 +19957,7 @@
         <v>7</v>
       </c>
       <c r="D935">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E935" t="s">
         <v>8</v>
@@ -19974,7 +19974,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E936" t="s">
         <v>8</v>
@@ -19991,7 +19991,7 @@
         <v>7</v>
       </c>
       <c r="D937">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E937" t="s">
         <v>8</v>
@@ -20008,7 +20008,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20059,7 +20059,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20076,7 +20076,7 @@
         <v>7</v>
       </c>
       <c r="D942">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E942" t="s">
         <v>8</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E943" t="s">
         <v>8</v>
@@ -20110,7 +20110,7 @@
         <v>7</v>
       </c>
       <c r="D944">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E944" t="s">
         <v>8</v>
@@ -20127,7 +20127,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20144,7 +20144,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20161,7 +20161,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20178,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20195,7 +20195,7 @@
         <v>7</v>
       </c>
       <c r="D949">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E949" t="s">
         <v>8</v>
@@ -20212,7 +20212,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20229,7 +20229,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20246,7 +20246,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20297,7 +20297,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20314,7 +20314,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20331,7 +20331,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E957" t="s">
         <v>8</v>
@@ -20365,7 +20365,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20382,7 +20382,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20399,7 +20399,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20416,7 +20416,7 @@
         <v>7</v>
       </c>
       <c r="D962">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E962" t="s">
         <v>8</v>
@@ -20433,7 +20433,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20450,7 +20450,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E964" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20484,7 +20484,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20501,7 +20501,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20518,7 +20518,7 @@
         <v>7</v>
       </c>
       <c r="D968">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E968" t="s">
         <v>8</v>
@@ -20535,7 +20535,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20552,7 +20552,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20569,7 +20569,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20586,7 +20586,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20620,7 +20620,7 @@
         <v>7</v>
       </c>
       <c r="D974">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E974" t="s">
         <v>8</v>
@@ -20637,7 +20637,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20654,7 +20654,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20671,7 +20671,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20688,7 +20688,7 @@
         <v>7</v>
       </c>
       <c r="D978">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E978" t="s">
         <v>8</v>
@@ -20705,7 +20705,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20722,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20739,7 +20739,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20756,7 +20756,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20773,7 +20773,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20790,7 +20790,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20807,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20824,7 +20824,7 @@
         <v>7</v>
       </c>
       <c r="D986">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E986" t="s">
         <v>8</v>
@@ -20841,7 +20841,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20858,7 +20858,7 @@
         <v>7</v>
       </c>
       <c r="D988">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E988" t="s">
         <v>8</v>
@@ -20875,7 +20875,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20892,7 +20892,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E990" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20926,7 +20926,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20960,7 +20960,7 @@
         <v>7</v>
       </c>
       <c r="D994">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E994" t="s">
         <v>8</v>
@@ -20994,7 +20994,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21028,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21045,7 +21045,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E999" t="s">
         <v>8</v>
@@ -21062,7 +21062,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21079,7 +21079,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21096,7 +21096,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21113,7 +21113,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21130,7 +21130,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21147,7 +21147,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21164,7 +21164,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21181,7 +21181,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21198,7 +21198,7 @@
         <v>7</v>
       </c>
       <c r="D1008">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1008" t="s">
         <v>8</v>
@@ -21215,7 +21215,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21232,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="D1010">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1010" t="s">
         <v>8</v>
@@ -21249,7 +21249,7 @@
         <v>7</v>
       </c>
       <c r="D1011">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1011" t="s">
         <v>8</v>
@@ -21266,7 +21266,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21283,7 +21283,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21300,7 +21300,7 @@
         <v>7</v>
       </c>
       <c r="D1014">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1014" t="s">
         <v>8</v>
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21368,7 +21368,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1018" t="s">
         <v>8</v>
@@ -21385,7 +21385,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21402,7 +21402,7 @@
         <v>7</v>
       </c>
       <c r="D1020">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1020" t="s">
         <v>8</v>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21436,7 +21436,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21453,7 +21453,7 @@
         <v>7</v>
       </c>
       <c r="D1023">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1023" t="s">
         <v>8</v>
@@ -21470,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21487,7 +21487,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21521,7 +21521,7 @@
         <v>7</v>
       </c>
       <c r="D1027">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1027" t="s">
         <v>8</v>
@@ -21538,7 +21538,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21555,7 +21555,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21572,7 +21572,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21589,7 +21589,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21606,7 +21606,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21623,7 +21623,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21640,7 +21640,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21657,7 +21657,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21691,7 +21691,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21725,7 +21725,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21742,7 +21742,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21759,7 +21759,7 @@
         <v>7</v>
       </c>
       <c r="D1041">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1041" t="s">
         <v>8</v>
@@ -21776,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21827,7 +21827,7 @@
         <v>7</v>
       </c>
       <c r="D1045">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1045" t="s">
         <v>8</v>
@@ -21861,7 +21861,7 @@
         <v>7</v>
       </c>
       <c r="D1047">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1047" t="s">
         <v>8</v>
@@ -21895,7 +21895,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21946,7 +21946,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21963,7 +21963,7 @@
         <v>7</v>
       </c>
       <c r="D1053">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1053" t="s">
         <v>8</v>
@@ -21980,7 +21980,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21997,7 +21997,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22014,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22048,7 +22048,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1058" t="s">
         <v>8</v>
@@ -22065,7 +22065,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22099,7 +22099,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22116,7 +22116,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22133,7 +22133,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22150,7 +22150,7 @@
         <v>7</v>
       </c>
       <c r="D1064">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1064" t="s">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22184,7 +22184,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22201,7 +22201,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22218,7 +22218,7 @@
         <v>7</v>
       </c>
       <c r="D1068">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1068" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22252,7 +22252,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22286,7 +22286,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22303,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22320,7 +22320,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22337,7 +22337,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22354,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22371,7 +22371,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22388,7 +22388,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22422,7 +22422,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22439,7 +22439,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22456,7 +22456,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22473,7 +22473,7 @@
         <v>7</v>
       </c>
       <c r="D1083">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1083" t="s">
         <v>8</v>
@@ -22490,7 +22490,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22507,7 +22507,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22524,7 +22524,7 @@
         <v>7</v>
       </c>
       <c r="D1086">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1086" t="s">
         <v>8</v>
@@ -22541,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22575,7 +22575,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22592,7 +22592,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22609,7 +22609,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22626,7 +22626,7 @@
         <v>7</v>
       </c>
       <c r="D1092">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1092" t="s">
         <v>8</v>
@@ -22643,7 +22643,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22660,7 +22660,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22694,7 +22694,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22745,7 +22745,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22762,7 +22762,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22779,7 +22779,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>99</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22896,7 +22896,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22966,7 +22966,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23050,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23064,7 +23064,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23148,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23288,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23302,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23428,7 +23428,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23582,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23610,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23750,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23806,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23862,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24044,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24142,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24170,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>72</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24254,7 +24254,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24282,7 +24282,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/selenium-report.xlsx
+++ b/reports/latest/selenium-report.xlsx
@@ -4096,7 +4096,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4130,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4181,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4249,7 +4249,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4317,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4368,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4436,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4453,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4470,7 +4470,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4589,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4674,7 +4674,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4691,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4708,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4759,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4793,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4827,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4861,7 +4861,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4912,7 +4912,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4946,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -4963,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5065,7 +5065,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5099,7 +5099,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
         <v>8<